--- a/EXCEL/M01/bus123-excel-m01-l01-starter.xlsx
+++ b/EXCEL/M01/bus123-excel-m01-l01-starter.xlsx
@@ -10,8 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorksheetBuild" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCTOR_AnswerKey" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -133,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -184,6 +183,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -724,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -745,8 +750,6 @@
           <t>Tidal Goods Co.</t>
         </is>
       </c>
-      <c r="G1" s="6" t="n"/>
-      <c r="H1" s="6" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -754,8 +757,6 @@
           <t>Main Activity: Create and Edit a Product Worksheet</t>
         </is>
       </c>
-      <c r="G2" s="6" t="n"/>
-      <c r="H2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="G3" s="6" t="n"/>
@@ -818,14 +819,14 @@
       <c r="D5" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="19" t="n"/>
       <c r="G5" s="11" t="n">
         <v>8.4</v>
       </c>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="13">
-        <f>IF(OR(E5="",F5="",H5=""),"",IF(AND(E5=12,F5=48,ABS(H5-403.2)&lt;=0.01),"Correct","Check"))</f>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="4">
+        <f>IF(OR(E5="",F5="",H5=""),"",IF(AND(F5=D5+E5,ABS(H5-F5*G5)&lt;=0.01),"Correct","Check"))</f>
         <v/>
       </c>
     </row>
@@ -843,14 +844,14 @@
       <c r="D6" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="19" t="n"/>
       <c r="G6" s="15" t="n">
         <v>6.75</v>
       </c>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="13">
-        <f>IF(OR(E6="",F6="",H6=""),"",IF(AND(E6=8,F6=36,ABS(H6-243.0)&lt;=0.01),"Correct","Check"))</f>
+      <c r="H6" s="20" t="n"/>
+      <c r="I6" s="4">
+        <f>IF(OR(E6="",F6="",H6=""),"",IF(AND(F6=D6+E6,ABS(H6-F6*G6)&lt;=0.01),"Correct","Check"))</f>
         <v/>
       </c>
     </row>
@@ -868,14 +869,14 @@
       <c r="D7" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="10" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="19" t="n"/>
       <c r="G7" s="11" t="n">
         <v>11.25</v>
       </c>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="13">
-        <f>IF(OR(E7="",F7="",H7=""),"",IF(AND(E7=6,F7=24,ABS(H7-270.0)&lt;=0.01),"Correct","Check"))</f>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="4">
+        <f>IF(OR(E7="",F7="",H7=""),"",IF(AND(F7=D7+E7,ABS(H7-F7*G7)&lt;=0.01),"Correct","Check"))</f>
         <v/>
       </c>
     </row>
@@ -893,14 +894,14 @@
       <c r="D8" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="19" t="n"/>
       <c r="G8" s="15" t="n">
         <v>4.1</v>
       </c>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="13">
-        <f>IF(OR(E8="",F8="",H8=""),"",IF(AND(E8=15,F8=57,ABS(H8-233.7)&lt;=0.01),"Correct","Check"))</f>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="4">
+        <f>IF(OR(E8="",F8="",H8=""),"",IF(AND(F8=D8+E8,ABS(H8-F8*G8)&lt;=0.01),"Correct","Check"))</f>
         <v/>
       </c>
     </row>
@@ -918,20 +919,33 @@
       <c r="D9" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
       <c r="G9" s="11" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="13">
-        <f>IF(OR(E9="",F9="",H9=""),"",IF(AND(E9=9,F9=33,ABS(H9-323.4)&lt;=0.01),"Correct","Check"))</f>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="4">
+        <f>IF(OR(E9="",F9="",H9=""),"",IF(AND(F9=D9+E9,ABS(H9-F9*G9)&lt;=0.01),"Correct","Check"))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="19" t="inlineStr"/>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="4">
+        <f>IF(OR(F10="",G10="",H10=""),"",IF(AND(ABS(F10-SUM(F5:F9))&lt;=0.01,ABS(G10-MAX(G5:G9))&lt;=0.01,ABS(H10-SUM(H5:H9))&lt;=0.01),"Correct","Check"))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="G11" s="6" t="n"/>
@@ -940,33 +954,41 @@
     <row r="12">
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>Manager Edit Request</t>
+          <t>Shipment Note</t>
         </is>
       </c>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="42" customHeight="1">
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>After completing the table, rename the activity tab to WorksheetBuild if needed and check that totals still make sense.</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-    </row>
+          <t>A new shipment arrived: Reusable bottle 12; Canvas tote 8; Desk organizer 6; Bamboo utensil set 15; Travel mug 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-    </row>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Manager Edit Request</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Complete the yellow cells. Use formulas for Updated Qty and Inventory Value, then add a summary row with total updated quantity, highest unit cost, and total inventory value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
   </sheetData>
-  <mergeCells count="3">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <mergeCells count="4">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B13:I15"/>
+    <mergeCell ref="B13:I14"/>
+    <mergeCell ref="B16:I17"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="I5:I9">
@@ -974,6 +996,14 @@
       <formula>"Correct"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Check"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:I10">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
+      <formula>"Correct"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
       <formula>"Check"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -987,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1014,15 +1044,16 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Prompt</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Student Entry</t>
+          <t>Where</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1037,38 +1068,62 @@
           <t>Total updated quantity</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="13">
-        <f>IF(C5="","",IF(ABS(C5-198)&lt;=0.01,"Correct","Check"))</f>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>WorksheetBuild!F10</t>
+        </is>
+      </c>
+      <c r="D5" s="4">
+        <f>IF(WorksheetBuild!F10="","",IF(ABS(WorksheetBuild!F10-SUM(WorksheetBuild!F5:F9))&lt;=0.01,"Correct","Check"))</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Total inventory value</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="13">
-        <f>IF(C6="","",IF(ABS(C6-1561.9)&lt;=0.01,"Correct","Check"))</f>
+          <t>Highest unit cost</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>WorksheetBuild!G10</t>
+        </is>
+      </c>
+      <c r="D6" s="4">
+        <f>IF(WorksheetBuild!G10="","",IF(ABS(WorksheetBuild!G10-MAX(WorksheetBuild!G5:G9))&lt;=0.01,"Correct","Check"))</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Highest unit cost</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="13">
-        <f>IF(C7="","",IF(ABS(C7-11.25)&lt;=0.01,"Correct","Check"))</f>
+          <t>Total inventory value</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>WorksheetBuild!H10</t>
+        </is>
+      </c>
+      <c r="D7" s="4">
+        <f>IF(WorksheetBuild!H10="","",IF(ABS(WorksheetBuild!H10-SUM(WorksheetBuild!H5:H9))&lt;=0.01,"Correct","Check"))</f>
         <v/>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9" ht="42" customHeight="1">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Use formulas, not typed totals. The check cells read your summary row on WorksheetBuild.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11"/>
   </sheetData>
-  <mergeCells count="2">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <mergeCells count="3">
+    <mergeCell ref="B9:D10"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -1079,248 +1134,18 @@
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"Check"</formula>
     </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
+      <formula>"Correct"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
+      <formula>"Check"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Instructor Solution</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>EXCEL-M01-L01 expected values</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Beginning Qty</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Units Added</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Updated Qty</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Unit Cost</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Inventory Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Reusable bottle</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Drinkware</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>403.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Canvas tote</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Desk organizer</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Home office</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Bamboo utensil set</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>233.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Travel mug</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Drinkware</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>323.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Formula Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>'=quantity*unit cost or price</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>'=basic summary formulas such as SUM, MAX, and COUNTIF</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/EXCEL/M01/bus123-excel-m01-l01-starter.xlsx
+++ b/EXCEL/M01/bus123-excel-m01-l01-starter.xlsx
@@ -4,9 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charge Analysis" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge - Payer Mix" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charge Analysis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge - Payer Mix" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -14,10 +15,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="\$#,##0"/>
+    <numFmt numFmtId="165" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -92,6 +94,22 @@
       <b val="1"/>
       <color rgb="FF355773"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF7A8290"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1A1F2C"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="18">
@@ -202,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -315,6 +333,43 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1091,7 +1146,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Work through the tabs left to right: Charge Analysis first, then the Payer Mix challenge.</t>
+          <t>Work through the tabs left to right: Live You Try It during the slide pauses, then Charge Analysis, then Challenge - Payer Mix.</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1156,7 @@
     <row r="18" ht="21.75" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  YELLOW cell  = your input. Type your formula here.</t>
+          <t xml:space="preserve">  YELLOW cell  = student entry. Type the slide givens, source data, or formula here.</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1180,7 @@
     <row r="22" ht="21.75" customHeight="1">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Figure out which function each task needs from the wording — the FormulaReferenceCard tab lists the syntax for every function you'll need.</t>
+          <t>Live You Try It is self-graded practice only. Charge Analysis and Challenge - Payer Mix are the submitted activity tabs; use the FormulaReferenceCard tab as your syntax guide.</t>
         </is>
       </c>
     </row>
@@ -1162,6 +1217,468 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="53" t="inlineStr">
+        <is>
+          <t>Live You Try It</t>
+        </is>
+      </c>
+      <c r="B1" s="54" t="n"/>
+      <c r="C1" s="54" t="n"/>
+      <c r="D1" s="54" t="n"/>
+      <c r="E1" s="54" t="n"/>
+      <c r="F1" s="54" t="n"/>
+      <c r="G1" s="54" t="n"/>
+      <c r="H1" s="54" t="n"/>
+    </row>
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="A2" s="55" t="inlineStr">
+        <is>
+          <t>Self-graded Excel pauses · enter slide givens first, then build formulas from those cells</t>
+        </is>
+      </c>
+      <c r="B2" s="54" t="n"/>
+      <c r="C2" s="54" t="n"/>
+      <c r="D2" s="54" t="n"/>
+      <c r="E2" s="54" t="n"/>
+      <c r="F2" s="54" t="n"/>
+      <c r="G2" s="54" t="n"/>
+      <c r="H2" s="54" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="13" t="n"/>
+      <c r="G3" s="13" t="n"/>
+      <c r="H3" s="13" t="n"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>Practice only: use these rows during the slide deck pauses. The feedback is for self-checking and is not part of the private graded rubric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1"/>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="B6" s="57" t="inlineStr">
+        <is>
+          <t>Pause 1 · SUM the slide charges</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Yellow entry cell</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Hint</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Cardiology charge</t>
+        </is>
+      </c>
+      <c r="C8" s="58" t="n"/>
+      <c r="D8" s="59" t="inlineStr">
+        <is>
+          <t>Slide 12 value</t>
+        </is>
+      </c>
+      <c r="G8" s="60">
+        <f>IF(C8="","Enter slide value",IF(C8=84200,"OK","Check slide 12"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Radiology charge</t>
+        </is>
+      </c>
+      <c r="C9" s="58" t="n"/>
+      <c r="D9" s="59" t="inlineStr">
+        <is>
+          <t>Slide 12 value</t>
+        </is>
+      </c>
+      <c r="G9" s="60">
+        <f>IF(C9="","Enter slide value",IF(C9=61500,"OK","Check slide 12"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Pediatrics charge</t>
+        </is>
+      </c>
+      <c r="C10" s="58" t="n"/>
+      <c r="D10" s="59" t="inlineStr">
+        <is>
+          <t>Slide 12 value</t>
+        </is>
+      </c>
+      <c r="G10" s="60">
+        <f>IF(C10="","Enter slide value",IF(C10=39800,"OK","Check slide 12"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Emergency charge</t>
+        </is>
+      </c>
+      <c r="C11" s="58" t="n"/>
+      <c r="D11" s="59" t="inlineStr">
+        <is>
+          <t>Slide 12 value</t>
+        </is>
+      </c>
+      <c r="G11" s="60">
+        <f>IF(C11="","Enter slide value",IF(C11=52500,"OK","Check slide 12"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Total monthly charges</t>
+        </is>
+      </c>
+      <c r="C12" s="58" t="n"/>
+      <c r="D12" s="59" t="inlineStr">
+        <is>
+          <t>Use =SUM(range) and reference the input cells above.</t>
+        </is>
+      </c>
+      <c r="G12" s="60">
+        <f>IF(C12="","Build a SUM formula",IF(ROUND(C12,0)=238000,"Correct","Recheck the SUM range"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1"/>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="B14" s="57" t="inlineStr">
+        <is>
+          <t>Pause 2 · Lock the reimbursement rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Yellow entry cell</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Hint</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>Contracted reimbursement rate</t>
+        </is>
+      </c>
+      <c r="C16" s="61" t="n"/>
+      <c r="D16" s="59" t="inlineStr">
+        <is>
+          <t>Slide 13 value</t>
+        </is>
+      </c>
+      <c r="G16" s="60">
+        <f>IF(C16="","Enter slide value",IF(ROUND(C16,2)=0.62,"OK","Check slide 13"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Cardiology charge</t>
+        </is>
+      </c>
+      <c r="C17" s="58" t="n"/>
+      <c r="D17" s="59" t="inlineStr">
+        <is>
+          <t>Slide 13 value</t>
+        </is>
+      </c>
+      <c r="G17" s="60">
+        <f>IF(C17="","Enter slide value",IF(C17=84200,"OK","Check slide 13"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Radiology charge</t>
+        </is>
+      </c>
+      <c r="C18" s="58" t="n"/>
+      <c r="D18" s="59" t="inlineStr">
+        <is>
+          <t>Slide 13 value</t>
+        </is>
+      </c>
+      <c r="G18" s="60">
+        <f>IF(C18="","Enter slide value",IF(C18=61500,"OK","Check slide 13"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Cardiology expected reimbursement</t>
+        </is>
+      </c>
+      <c r="C19" s="58" t="n"/>
+      <c r="D19" s="59" t="inlineStr">
+        <is>
+          <t>Reference the charge, then lock the rate with $.</t>
+        </is>
+      </c>
+      <c r="G19" s="60">
+        <f>IF(C19="","Build the formula",IF(ROUND(C19,0)=52204,"Correct","Did you lock the rate?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Radiology expected reimbursement</t>
+        </is>
+      </c>
+      <c r="C20" s="58" t="n"/>
+      <c r="D20" s="59" t="inlineStr">
+        <is>
+          <t>Copy the formula down and keep the rate fixed.</t>
+        </is>
+      </c>
+      <c r="G20" s="60">
+        <f>IF(C20="","Copy or build the formula",IF(ROUND(C20,0)=38130,"Correct","Did the rate stay put?"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1"/>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="B22" s="57" t="inlineStr">
+        <is>
+          <t>Pause 3 · Payer mix percent check</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Yellow entry cell</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Hint</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Medicare share</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="59" t="inlineStr">
+        <is>
+          <t>Slide 15 value</t>
+        </is>
+      </c>
+      <c r="G24" s="60">
+        <f>IF(C24="","Enter slide value",IF(ROUND(C24,2)=0.41,"OK","Check slide 15"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Medicaid share</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="59" t="inlineStr">
+        <is>
+          <t>Slide 15 value</t>
+        </is>
+      </c>
+      <c r="G25" s="60">
+        <f>IF(C25="","Enter slide value",IF(ROUND(C25,2)=0.23,"OK","Check slide 15"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Commercial share</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="59" t="inlineStr">
+        <is>
+          <t>Slide 15 value</t>
+        </is>
+      </c>
+      <c r="G26" s="60">
+        <f>IF(C26="","Enter slide value",IF(ROUND(C26,2)=0.28,"OK","Check slide 15"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Self-pay share</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="n"/>
+      <c r="D27" s="59" t="inlineStr">
+        <is>
+          <t>Slide 15 value</t>
+        </is>
+      </c>
+      <c r="G27" s="60">
+        <f>IF(C27="","Enter slide value",IF(ROUND(C27,2)=0.08,"OK","Check slide 15"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Total payer mix</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="59" t="inlineStr">
+        <is>
+          <t>Use SUM to verify the mix totals 100%.</t>
+        </is>
+      </c>
+      <c r="G28" s="60">
+        <f>IF(C28="","Build a SUM formula",IF(ROUND(C28,4)=1,"Correct","The mix should total 100%"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Largest payer share</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="n"/>
+      <c r="D29" s="59" t="inlineStr">
+        <is>
+          <t>Use MAX to identify the biggest share.</t>
+        </is>
+      </c>
+      <c r="G29" s="60">
+        <f>IF(C29="","Build a MAX formula",IF(ROUND(C29,2)=0.41,"Correct","Recheck the payer shares"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D19:F19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
@@ -1293,7 +1810,7 @@
           <t>Total monthly charges</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n"/>
+      <c r="C13" s="58" t="n"/>
       <c r="G13" s="20" t="inlineStr">
         <is>
           <t>Add every department's charges.</t>
@@ -1306,7 +1823,7 @@
           <t>Average charges per dept</t>
         </is>
       </c>
-      <c r="C14" s="19" t="n"/>
+      <c r="C14" s="58" t="n"/>
       <c r="G14" s="20" t="inlineStr">
         <is>
           <t>The mean across departments.</t>
@@ -1332,7 +1849,7 @@
           <t>Highest department charge</t>
         </is>
       </c>
-      <c r="C16" s="19" t="n"/>
+      <c r="C16" s="58" t="n"/>
       <c r="G16" s="20" t="inlineStr">
         <is>
           <t>The single largest value.</t>
@@ -1345,7 +1862,7 @@
           <t>Lowest department charge</t>
         </is>
       </c>
-      <c r="C17" s="19" t="n"/>
+      <c r="C17" s="58" t="n"/>
       <c r="G17" s="20" t="inlineStr">
         <is>
           <t>The single smallest value.</t>
@@ -1400,7 +1917,7 @@
       <c r="C23" s="16" t="n">
         <v>84200</v>
       </c>
-      <c r="D23" s="19" t="n"/>
+      <c r="D23" s="58" t="n"/>
       <c r="G23" s="24" t="inlineStr">
         <is>
           <t>Build the first row, then copy it down. Did the rate stay put?</t>
@@ -1416,7 +1933,7 @@
       <c r="C24" s="16" t="n">
         <v>61500</v>
       </c>
-      <c r="D24" s="19" t="n"/>
+      <c r="D24" s="58" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="15" t="inlineStr">
@@ -1427,7 +1944,7 @@
       <c r="C25" s="16" t="n">
         <v>39800</v>
       </c>
-      <c r="D25" s="19" t="n"/>
+      <c r="D25" s="58" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="15" t="inlineStr">
@@ -1438,7 +1955,7 @@
       <c r="C26" s="16" t="n">
         <v>52500</v>
       </c>
-      <c r="D26" s="19" t="n"/>
+      <c r="D26" s="58" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="15" t="inlineStr">
@@ -1449,7 +1966,7 @@
       <c r="C27" s="16" t="n">
         <v>47300</v>
       </c>
-      <c r="D27" s="19" t="n"/>
+      <c r="D27" s="58" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1542,7 +2059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1728,140 +2245,220 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21.11000061035156" customWidth="1" min="1" max="1"/>
-    <col width="25.55999946594238" customWidth="1" min="2" max="2"/>
-    <col width="34.43999862670898" customWidth="1" min="3" max="3"/>
-    <col width="33.33000183105469" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="B1" s="45" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>Excel Pattern</t>
         </is>
       </c>
-      <c r="C1" s="45" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>Plain-English Meaning</t>
         </is>
       </c>
-      <c r="D1" s="45" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>Watch Out For</t>
         </is>
       </c>
     </row>
     <row r="2" ht="31.5" customHeight="1">
-      <c r="A2" s="49" t="inlineStr">
+      <c r="A2" s="63" t="inlineStr">
         <is>
           <t>Total a range</t>
         </is>
       </c>
-      <c r="B2" s="51" t="inlineStr">
-        <is>
-          <t>=SUM(C2:C5)</t>
-        </is>
-      </c>
-      <c r="C2" s="49" t="inlineStr">
+      <c r="B2" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> =SUM(C6:C10)</t>
+        </is>
+      </c>
+      <c r="C2" s="63" t="inlineStr">
         <is>
           <t>Adds selected numbers into one total.</t>
         </is>
       </c>
-      <c r="D2" s="52" t="inlineStr">
+      <c r="D2" s="65" t="inlineStr">
         <is>
           <t>Use a range instead of typing each charge.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="31.5" customHeight="1">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="63" t="inlineStr">
         <is>
           <t>Average a range</t>
         </is>
       </c>
-      <c r="B3" s="51" t="inlineStr">
-        <is>
-          <t>=AVERAGE(C2:C5)</t>
-        </is>
-      </c>
-      <c r="C3" s="49" t="inlineStr">
+      <c r="B3" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> =AVERAGE(C6:C10)</t>
+        </is>
+      </c>
+      <c r="C3" s="63" t="inlineStr">
         <is>
           <t>Finds the typical value from several numbers.</t>
         </is>
       </c>
-      <c r="D3" s="52" t="inlineStr">
+      <c r="D3" s="65" t="inlineStr">
         <is>
           <t>Average is not the same as total.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="63" t="inlineStr">
         <is>
           <t>Count numeric cells</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr">
-        <is>
-          <t>=COUNT(C2:C5)</t>
-        </is>
-      </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="B4" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> =COUNT(C6:C10)</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="inlineStr">
         <is>
           <t>Counts cells that contain numbers.</t>
         </is>
       </c>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="D4" s="65" t="inlineStr">
         <is>
           <t>Text labels are ignored.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="63" t="inlineStr">
+        <is>
+          <t>Highest value</t>
+        </is>
+      </c>
+      <c r="B5" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> =MAX(C6:C10)</t>
+        </is>
+      </c>
+      <c r="C5" s="63" t="inlineStr">
+        <is>
+          <t>Returns the largest value in a range.</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="inlineStr">
+        <is>
+          <t>MAX finds the biggest number, not the biggest label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1">
+      <c r="A6" s="63" t="inlineStr">
+        <is>
+          <t>Lowest value</t>
+        </is>
+      </c>
+      <c r="B6" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> =MIN(C6:C10)</t>
+        </is>
+      </c>
+      <c r="C6" s="63" t="inlineStr">
+        <is>
+          <t>Returns the smallest value in a range.</t>
+        </is>
+      </c>
+      <c r="D6" s="65" t="inlineStr">
+        <is>
+          <t>MIN finds the smallest number, not the smallest label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="31.5" customHeight="1">
+      <c r="A7" s="63" t="inlineStr">
         <is>
           <t>Percent of total</t>
         </is>
       </c>
-      <c r="B5" s="51" t="inlineStr">
-        <is>
-          <t>=C2/$C$6</t>
-        </is>
-      </c>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> =C6/$C$10</t>
+        </is>
+      </c>
+      <c r="C7" s="63" t="inlineStr">
         <is>
           <t>Shows one value as a share of the total.</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D7" s="65" t="inlineStr">
         <is>
           <t>Lock the total before copying.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="21.75" customHeight="1"/>
-    <row r="7" ht="21.75" customHeight="1"/>
-    <row r="8" ht="21.75" customHeight="1"/>
-    <row r="9" ht="21.75" customHeight="1"/>
-    <row r="10" ht="21.75" customHeight="1"/>
-    <row r="11" ht="21.75" customHeight="1"/>
-    <row r="12" ht="21.75" customHeight="1"/>
-    <row r="13" ht="21.75" customHeight="1"/>
+    <row r="8" ht="31.5" customHeight="1">
+      <c r="A8" s="63" t="inlineStr">
+        <is>
+          <t>Absolute reference</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> $C$21 or $C$10</t>
+        </is>
+      </c>
+      <c r="C8" s="63" t="inlineStr">
+        <is>
+          <t>Locks a shared input so copied formulas keep using it.</t>
+        </is>
+      </c>
+      <c r="D8" s="65" t="inlineStr">
+        <is>
+          <t>Press F4 to toggle dollar signs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="31.5" customHeight="1">
+      <c r="A9" s="63" t="inlineStr">
+        <is>
+          <t>Range notation</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="inlineStr">
+        <is>
+          <t>C6:C10</t>
+        </is>
+      </c>
+      <c r="C9" s="63" t="inlineStr">
+        <is>
+          <t>Means cell C6 through cell C10.</t>
+        </is>
+      </c>
+      <c r="D9" s="65" t="inlineStr">
+        <is>
+          <t>Include only the cells you want calculated.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>